--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.35.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -596,21 +596,25 @@
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): amendedBill (odd internal casing) :: amendedBill r A Ã€</t>
+          <t>L44: suspicious token(s): amendedBill (odd internal casing) :: amendedBill r A À</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ na to rejoin is n</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): amendedBill (odd internal casing) :: amendedBill r A Ã€</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L13: isolated marker/symbol line :: 28</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: I-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -628,7 +632,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • We command you, that within days after the</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: with by Subp Ã¦ na to hea</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: As respects such Defendant, the writ is as follows :â€” %</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • We command you, that within days after the</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: , /</t>
+          <t>L30: isolated marker/symbol line :: I-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -717,16 +725,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ ena to hear Judgment, as hereafter shown.</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ We command you, that within days after the</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 1</t>
+          <t>L32: isolated marker/symbol line :: , /</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,16 +772,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: subp Ã¦ na to</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Plaintiffâ€™s Solicitor.</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -791,7 +783,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 1850.</t>
+          <t>L34: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -827,16 +819,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: orm of the subp Ã¦ ena to answer an amended bill</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: liberty to file his rÃ©plication.!</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -846,7 +830,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 1%</t>
+          <t>L59: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -882,11 +866,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -897,7 +877,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: -A</t>
+          <t>L65: isolated marker/symbol line :: 1%</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -933,22 +913,18 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: I</t>
+          <t>L69: isolated marker/symbol line :: -A</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -990,10 +966,14 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
-      <c r="O9" s="1" t="inlineStr"/>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>L94: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1013,12 +993,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1033,7 +1013,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: ,</t>
+          <t>L68: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1061,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1076,7 +1056,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 185</t>
+          <t>L69: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1099,12 +1079,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1119,7 +1099,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 0</t>
+          <t>L78: isolated marker/symbol line :: 185</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1160,7 +1140,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L81: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1186,7 +1170,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
